--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -61,6 +64,30 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
     <t>1S</t>
   </si>
   <si>
@@ -70,10 +97,37 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>13:47</t>
-  </si>
-  <si>
-    <t>10:32</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:47:00</t>
+  </si>
+  <si>
+    <t>10:31:00</t>
+  </si>
+  <si>
+    <t>08:48:00</t>
+  </si>
+  <si>
+    <t>11:36:00</t>
+  </si>
+  <si>
+    <t>17:34:00</t>
+  </si>
+  <si>
+    <t>3231448756 3231448756</t>
+  </si>
+  <si>
+    <t>3231931967 3231931967</t>
+  </si>
+  <si>
+    <t>3232398599 3232398599</t>
+  </si>
+  <si>
+    <t>3232574822 3232574822</t>
+  </si>
+  <si>
+    <t>3232609203 3232609203</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ</t>
@@ -497,24 +551,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,160 +610,301 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1146</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>66.67</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>110.67</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>120.01</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>127937</v>
+      <c r="N2" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1199</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>62.94</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
         <v>1.64</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>103.22</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.76</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>110.77</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>266984</v>
+      <c r="N3" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>60.58</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4">
+        <v>1.63</v>
+      </c>
+      <c r="I4" s="1">
+        <v>98.75</v>
+      </c>
+      <c r="J4">
+        <v>1.72</v>
+      </c>
+      <c r="K4" s="1">
+        <v>104.2</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>28.41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <v>1.62</v>
+      </c>
+      <c r="I5" s="1">
+        <v>46.02</v>
+      </c>
+      <c r="J5">
+        <v>1.7</v>
+      </c>
+      <c r="K5" s="1">
+        <v>48.3</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6">
+        <v>53.98</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6">
+        <v>1.62</v>
+      </c>
+      <c r="I6" s="1">
+        <v>87.45</v>
+      </c>
+      <c r="J6">
+        <v>1.71</v>
+      </c>
+      <c r="K6" s="1">
+        <v>92.31</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6">
-        <v>129.61</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.6503</v>
-      </c>
-      <c r="E8" s="6">
-        <v>213.89</v>
-      </c>
-      <c r="F8" s="6">
-        <v>230.78</v>
-      </c>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="9">
-        <v>129.61</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>213.89</v>
-      </c>
-      <c r="F9" s="9">
-        <v>230.78</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="6">
+        <v>272.58</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.6366</v>
+      </c>
+      <c r="E11" s="6">
+        <v>446.11</v>
+      </c>
+      <c r="F11" s="6">
+        <v>475.59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="9">
+        <v>272.58</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9">
+        <v>446.11</v>
+      </c>
+      <c r="F12" s="9">
+        <v>475.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
@@ -181,7 +181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,12 +191,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -246,17 +240,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,85 +46,34 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1195 243 Тракия Езеро</t>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Кърджали 1</t>
   </si>
   <si>
     <t>1S</t>
   </si>
   <si>
+    <t>2S</t>
+  </si>
+  <si>
     <t>78970153027720720</t>
   </si>
   <si>
+    <t>78970153027720738</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:47:00</t>
-  </si>
-  <si>
-    <t>10:31:00</t>
-  </si>
-  <si>
-    <t>08:48:00</t>
-  </si>
-  <si>
-    <t>11:36:00</t>
-  </si>
-  <si>
-    <t>17:34:00</t>
-  </si>
-  <si>
-    <t>3231448756 3231448756</t>
-  </si>
-  <si>
-    <t>3231931967 3231931967</t>
-  </si>
-  <si>
-    <t>3232398599 3232398599</t>
-  </si>
-  <si>
-    <t>3232574822 3232574822</t>
-  </si>
-  <si>
-    <t>3232609203 3232609203</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ</t>
@@ -545,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -554,17 +500,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -598,307 +541,148 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>66.73</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H2">
+        <v>107.44</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J2">
+        <v>110.77</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>33.25</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H3">
+        <v>53.53</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="J3">
+        <v>52.87</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B8" s="6">
+        <v>99.98</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.61</v>
+      </c>
+      <c r="E8" s="6">
+        <v>160.97</v>
+      </c>
+      <c r="F8" s="6">
+        <v>163.64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2">
-        <v>66.67</v>
-      </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2">
-        <v>1.66</v>
-      </c>
-      <c r="I2" s="1">
-        <v>110.67</v>
-      </c>
-      <c r="J2">
-        <v>1.8</v>
-      </c>
-      <c r="K2" s="1">
-        <v>120.01</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3">
-        <v>62.94</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
-        <v>1.64</v>
-      </c>
-      <c r="I3" s="1">
-        <v>103.22</v>
-      </c>
-      <c r="J3">
-        <v>1.76</v>
-      </c>
-      <c r="K3" s="1">
-        <v>110.77</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4">
-        <v>60.58</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4">
-        <v>1.63</v>
-      </c>
-      <c r="I4" s="1">
-        <v>98.75</v>
-      </c>
-      <c r="J4">
-        <v>1.72</v>
-      </c>
-      <c r="K4" s="1">
-        <v>104.2</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5">
-        <v>28.41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5">
-        <v>1.62</v>
-      </c>
-      <c r="I5" s="1">
-        <v>46.02</v>
-      </c>
-      <c r="J5">
-        <v>1.7</v>
-      </c>
-      <c r="K5" s="1">
-        <v>48.3</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6">
-        <v>53.98</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6">
-        <v>1.62</v>
-      </c>
-      <c r="I6" s="1">
-        <v>87.45</v>
-      </c>
-      <c r="J6">
-        <v>1.71</v>
-      </c>
-      <c r="K6" s="1">
-        <v>92.31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="6">
-        <v>272.58</v>
-      </c>
-      <c r="C11" s="6">
-        <v>5</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.6366</v>
-      </c>
-      <c r="E11" s="6">
-        <v>446.11</v>
-      </c>
-      <c r="F11" s="6">
-        <v>475.59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="9">
-        <v>272.58</v>
-      </c>
-      <c r="C12" s="9">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>446.11</v>
-      </c>
-      <c r="F12" s="9">
-        <v>475.59</v>
+      <c r="B9" s="9">
+        <v>99.98</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9">
+        <v>160.97</v>
+      </c>
+      <c r="F9" s="9">
+        <v>163.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-04</t>
   </si>
   <si>
@@ -61,16 +70,19 @@
     <t>2026-06-22</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Кърджали 1</t>
-  </si>
-  <si>
-    <t>Хасково</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1922 Kardzhali Belomorski</t>
+  </si>
+  <si>
+    <t>1909 О5, Хасково</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>1S</t>
@@ -88,16 +100,37 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-04 18:49:24</t>
-  </si>
-  <si>
-    <t>2026-06-14 16:39:51</t>
-  </si>
-  <si>
-    <t>2026-06-21 12:15:35</t>
-  </si>
-  <si>
-    <t>2026-06-22 09:04:34</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>18:49:00</t>
+  </si>
+  <si>
+    <t>16:39:00</t>
+  </si>
+  <si>
+    <t>12:15:00</t>
+  </si>
+  <si>
+    <t>09:04:00</t>
+  </si>
+  <si>
+    <t>17:19:00</t>
+  </si>
+  <si>
+    <t>3232866641 3232866641</t>
+  </si>
+  <si>
+    <t>3233354656 3233354656</t>
+  </si>
+  <si>
+    <t>3233686738 3233686738</t>
+  </si>
+  <si>
+    <t>3233715526 3233715526</t>
+  </si>
+  <si>
+    <t>3234015040 3234015040</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ</t>
@@ -515,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -524,14 +557,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -565,218 +601,307 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>66.73</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
         <v>1.58</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>105.43</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>110.77</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>33.25</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3">
         <v>1.55</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>51.54</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.59</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>52.87</v>
       </c>
-      <c r="K3" t="s">
-        <v>25</v>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>40</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
         <v>1.51</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>60.4</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.54</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>61.6</v>
       </c>
-      <c r="K4" t="s">
-        <v>26</v>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F5">
         <v>58.04</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
         <v>1.48</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>85.90000000000001</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.52</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>88.22</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
+      <c r="F6">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6">
+        <v>1.45</v>
+      </c>
+      <c r="I6" s="1">
+        <v>96.41</v>
+      </c>
+      <c r="J6">
+        <v>1.51</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100.4</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="6">
-        <v>198.02</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.5315</v>
-      </c>
-      <c r="E10" s="6">
-        <v>303.27</v>
-      </c>
-      <c r="F10" s="6">
-        <v>313.46</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6">
+        <v>264.51</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.511</v>
+      </c>
+      <c r="E11" s="6">
+        <v>399.68</v>
+      </c>
+      <c r="F11" s="6">
+        <v>413.86</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="9">
-        <v>198.02</v>
-      </c>
-      <c r="C11" s="9">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9">
-        <v>303.27</v>
-      </c>
-      <c r="F11" s="9">
-        <v>313.46</v>
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="9">
+        <v>264.51</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9">
+        <v>399.68</v>
+      </c>
+      <c r="F12" s="9">
+        <v>413.86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,28 +55,88 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-03</t>
   </si>
   <si>
     <t>2026-07-09</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>1S</t>
   </si>
   <si>
+    <t>2S</t>
+  </si>
+  <si>
     <t>78970153027720720</t>
   </si>
   <si>
+    <t>78970153027720738</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-03 12:42:50</t>
-  </si>
-  <si>
-    <t>2026-07-09 15:03:57</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>12:43:00</t>
+  </si>
+  <si>
+    <t>15:04:00</t>
+  </si>
+  <si>
+    <t>17:46:00</t>
+  </si>
+  <si>
+    <t>09:08:00</t>
+  </si>
+  <si>
+    <t>15:34:00</t>
+  </si>
+  <si>
+    <t>11:12:00</t>
+  </si>
+  <si>
+    <t>3234247750 3234247750</t>
+  </si>
+  <si>
+    <t>3234539832 3234539832</t>
+  </si>
+  <si>
+    <t>3234892218 3234892218</t>
+  </si>
+  <si>
+    <t>3234941131 3234941131</t>
+  </si>
+  <si>
+    <t>3235352627 3235352627</t>
+  </si>
+  <si>
+    <t>3235572549 3235572549</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ</t>
@@ -491,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,15 +563,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,154 +610,348 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>55.62</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>80.09</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>83.98999999999999</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>55.08</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3">
         <v>1.45</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>79.87</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>83.72</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <v>1.54</v>
+      </c>
+      <c r="I4" s="1">
+        <v>77</v>
+      </c>
+      <c r="J4">
+        <v>1.62</v>
+      </c>
+      <c r="K4" s="1">
+        <v>81</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>58.79</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>1.54</v>
+      </c>
+      <c r="I5" s="1">
+        <v>90.54000000000001</v>
+      </c>
+      <c r="J5">
+        <v>1.63</v>
+      </c>
+      <c r="K5" s="1">
+        <v>95.83</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>51.85</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6">
+        <v>1.66</v>
+      </c>
+      <c r="I6" s="1">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="J6">
+        <v>1.74</v>
+      </c>
+      <c r="K6" s="1">
+        <v>90.22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>45.16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>1.71</v>
+      </c>
+      <c r="I7" s="1">
+        <v>77.22</v>
+      </c>
+      <c r="J7">
+        <v>1.76</v>
+      </c>
+      <c r="K7" s="1">
+        <v>79.48</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6">
-        <v>110.7</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.445</v>
-      </c>
-      <c r="E8" s="6">
-        <v>159.96</v>
-      </c>
-      <c r="F8" s="6">
-        <v>167.71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="9">
-        <v>110.7</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>159.96</v>
-      </c>
-      <c r="F9" s="9">
-        <v>167.71</v>
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6">
+        <v>316.5</v>
+      </c>
+      <c r="C12" s="6">
+        <v>6</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.5507</v>
+      </c>
+      <c r="E12" s="6">
+        <v>490.79</v>
+      </c>
+      <c r="F12" s="6">
+        <v>514.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="9">
+        <v>316.5</v>
+      </c>
+      <c r="C13" s="9">
+        <v>6</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="9">
+        <v>490.79</v>
+      </c>
+      <c r="F13" s="9">
+        <v>514.24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
@@ -163,7 +163,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -922,7 +922,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="7">
-        <v>1.5507</v>
+        <v>1.550679</v>
       </c>
       <c r="E12" s="6">
         <v>490.79</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -554,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -567,13 +570,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -616,274 +619,295 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2">
+        <v>55.623</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.439</v>
+      </c>
+      <c r="J2">
+        <v>80.04149700000001</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L2" s="1">
+        <v>83.99073</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
+        <v>55.079</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3">
+        <v>1.412</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="J3">
+        <v>79.97470800000001</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L3" s="1">
+        <v>83.72008</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="F2">
-        <v>55.62</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E4" t="s">
         <v>28</v>
-      </c>
-      <c r="H2">
-        <v>1.44</v>
-      </c>
-      <c r="I2" s="1">
-        <v>80.09</v>
-      </c>
-      <c r="J2">
-        <v>1.51</v>
-      </c>
-      <c r="K2" s="1">
-        <v>83.98999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3">
-        <v>55.08</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3">
-        <v>1.45</v>
-      </c>
-      <c r="I3" s="1">
-        <v>79.87</v>
-      </c>
-      <c r="J3">
-        <v>1.52</v>
-      </c>
-      <c r="K3" s="1">
-        <v>83.72</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
       <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4">
+        <v>1.499</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.539</v>
+      </c>
+      <c r="J4">
+        <v>76.95</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="L4" s="1">
+        <v>81</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="H4">
-        <v>1.54</v>
-      </c>
-      <c r="I4" s="1">
-        <v>77</v>
-      </c>
-      <c r="J4">
-        <v>1.62</v>
-      </c>
-      <c r="K4" s="1">
-        <v>81</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4">
+      <c r="F5">
+        <v>58.791</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
+        <v>1.499</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.539</v>
+      </c>
+      <c r="J5">
+        <v>90.479349</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="L5" s="1">
+        <v>95.82933</v>
+      </c>
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="O5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>58.79</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="H5">
-        <v>1.54</v>
-      </c>
-      <c r="I5" s="1">
-        <v>90.54000000000001</v>
-      </c>
-      <c r="J5">
-        <v>1.63</v>
-      </c>
-      <c r="K5" s="1">
-        <v>95.83</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
+      <c r="F6">
+        <v>51.851</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6">
+        <v>1.619</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.659</v>
+      </c>
+      <c r="J6">
+        <v>86.020809</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L6" s="1">
+        <v>90.22074000000001</v>
+      </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6">
-        <v>51.85</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="H6">
-        <v>1.66</v>
-      </c>
-      <c r="I6" s="1">
-        <v>86.06999999999999</v>
-      </c>
-      <c r="J6">
-        <v>1.74</v>
-      </c>
-      <c r="K6" s="1">
-        <v>90.22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6">
+      <c r="F7">
+        <v>45.159</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7">
+        <v>1.674</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.714</v>
+      </c>
+      <c r="J7">
+        <v>77.40252599999999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L7" s="1">
+        <v>79.47984</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7">
-        <v>45.16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>1.71</v>
-      </c>
-      <c r="I7" s="1">
-        <v>77.22</v>
-      </c>
-      <c r="J7">
-        <v>1.76</v>
-      </c>
-      <c r="K7" s="1">
-        <v>79.48</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -891,59 +915,59 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="6">
-        <v>316.5</v>
+        <v>316.503</v>
       </c>
       <c r="C12" s="6">
         <v>6</v>
       </c>
       <c r="D12" s="7">
-        <v>1.550679</v>
+        <v>1.550914</v>
       </c>
       <c r="E12" s="6">
-        <v>490.79</v>
+        <v>490.87</v>
       </c>
       <c r="F12" s="6">
         <v>514.24</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="9">
-        <v>316.5</v>
+        <v>316.503</v>
       </c>
       <c r="C13" s="9">
         <v>6</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="9">
-        <v>490.79</v>
+        <v>490.87</v>
       </c>
       <c r="F13" s="9">
         <v>514.24</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ/СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -165,8 +162,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -259,10 +256,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -570,13 +567,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -619,295 +616,274 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>55.623</v>
       </c>
       <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
+        <v>1.439</v>
+      </c>
+      <c r="I2" s="1">
+        <v>80.041</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>83.991</v>
+      </c>
+      <c r="L2" t="s">
         <v>29</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.439</v>
-      </c>
-      <c r="J2">
-        <v>80.04149700000001</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>83.99073</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>55.079</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>1.412</v>
+        <v>1.452</v>
       </c>
       <c r="I3" s="1">
-        <v>1.452</v>
+        <v>79.97499999999999</v>
       </c>
       <c r="J3">
-        <v>79.97470800000001</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L3" s="1">
-        <v>83.72008</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3">
+        <v>83.72</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I4" s="1">
-        <v>1.539</v>
+        <v>76.95</v>
       </c>
       <c r="J4">
-        <v>76.95</v>
+        <v>1.62</v>
       </c>
       <c r="K4" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="L4" s="1">
         <v>81</v>
       </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5">
         <v>58.791</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I5" s="1">
-        <v>1.539</v>
+        <v>90.479</v>
       </c>
       <c r="J5">
-        <v>90.479349</v>
+        <v>1.63</v>
       </c>
       <c r="K5" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L5" s="1">
-        <v>95.82933</v>
-      </c>
-      <c r="M5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5">
+        <v>95.82899999999999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>51.851</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>1.619</v>
+        <v>1.659</v>
       </c>
       <c r="I6" s="1">
-        <v>1.659</v>
+        <v>86.021</v>
       </c>
       <c r="J6">
-        <v>86.020809</v>
+        <v>1.74</v>
       </c>
       <c r="K6" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L6" s="1">
-        <v>90.22074000000001</v>
-      </c>
-      <c r="M6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6">
+        <v>90.221</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>45.159</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7">
-        <v>1.674</v>
+        <v>1.714</v>
       </c>
       <c r="I7" s="1">
-        <v>1.714</v>
+        <v>77.40300000000001</v>
       </c>
       <c r="J7">
-        <v>77.40252599999999</v>
+        <v>1.76</v>
       </c>
       <c r="K7" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L7" s="1">
-        <v>79.47984</v>
-      </c>
-      <c r="M7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7">
+        <v>79.48</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -915,49 +891,49 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="6">
         <v>316.503</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>6</v>
       </c>
       <c r="D12" s="7">
-        <v>1.550914</v>
-      </c>
-      <c r="E12" s="6">
-        <v>490.87</v>
-      </c>
-      <c r="F12" s="6">
-        <v>514.24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>1.551</v>
+      </c>
+      <c r="E12" s="7">
+        <v>490.869</v>
+      </c>
+      <c r="F12" s="7">
+        <v>514.241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="9">
         <v>316.503</v>
@@ -967,10 +943,10 @@
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="9">
-        <v>490.87</v>
+        <v>490.869</v>
       </c>
       <c r="F13" s="9">
-        <v>514.24</v>
+        <v>514.241</v>
       </c>
     </row>
   </sheetData>
